--- a/data/raw/btex_litsummary.xlsx
+++ b/data/raw/btex_litsummary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Research/South Philly R21/Analysis/source_apportionment/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drexel0-my.sharepoint.com/personal/lf649_drexel_edu/Documents/Research/South Philly R21/Papers/Analysis Paper/thriveair_analysis/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1297" documentId="8_{2049016A-0404-0B44-8FE3-08B7ECB37F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C40E938-01B4-4C9E-99FB-7AC026CD5D3A}"/>
+  <xr:revisionPtr revIDLastSave="1299" documentId="8_{2049016A-0404-0B44-8FE3-08B7ECB37F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{047022B0-8940-47EC-B428-A700887E9D12}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E984BCCB-5BDC-4843-A853-76F01789C100}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{E984BCCB-5BDC-4843-A853-76F01789C100}"/>
   </bookViews>
   <sheets>
     <sheet name="passive mgm3" sheetId="1" r:id="rId1"/>
@@ -1186,228 +1186,228 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
         <v>116</v>
       </c>
       <c r="F2">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>147</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K2" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="L2">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="M2">
-        <v>0.76</v>
+        <v>1.6</v>
       </c>
       <c r="N2">
-        <v>2.87</v>
+        <v>7</v>
       </c>
       <c r="O2">
-        <v>0.47</v>
+        <v>0.9</v>
       </c>
       <c r="P2">
-        <v>1.33</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="Q2">
-        <v>0.47</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
         <v>116</v>
       </c>
       <c r="F3">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>147</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" t="s">
         <v>173</v>
       </c>
       <c r="K3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L3">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="M3">
-        <v>0.98</v>
+        <v>3.86</v>
       </c>
       <c r="N3">
-        <v>2.5099999999999998</v>
+        <v>27.7</v>
       </c>
       <c r="O3">
-        <v>0.48</v>
+        <v>9.1300000000000008</v>
       </c>
       <c r="P3">
-        <v>1.28</v>
+        <v>13.87</v>
       </c>
       <c r="Q3">
-        <v>0.49</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>147</v>
       </c>
       <c r="H4" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K4" t="s">
-        <v>131</v>
-      </c>
-      <c r="L4">
-        <v>2009</v>
+        <v>129</v>
+      </c>
+      <c r="L4" t="s">
+        <v>103</v>
       </c>
       <c r="M4">
-        <v>16.7</v>
+        <v>89</v>
       </c>
       <c r="N4">
-        <v>40.5</v>
+        <v>204</v>
       </c>
       <c r="O4">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="P4">
-        <v>24.4</v>
+        <v>61</v>
       </c>
       <c r="Q4">
-        <v>7.9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" t="s">
         <v>147</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K5" t="s">
-        <v>131</v>
-      </c>
-      <c r="L5">
-        <v>2009</v>
+        <v>129</v>
+      </c>
+      <c r="L5" t="s">
+        <v>103</v>
       </c>
       <c r="M5">
-        <v>2.7</v>
+        <v>48</v>
       </c>
       <c r="N5">
-        <v>9.6999999999999993</v>
+        <v>85</v>
       </c>
       <c r="O5">
-        <v>2.5</v>
+        <v>7</v>
       </c>
       <c r="P5">
-        <v>6.1</v>
+        <v>30</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E6" t="s">
         <v>116</v>
@@ -1422,219 +1422,219 @@
         <v>133</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="K6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L6">
-        <v>2016</v>
+        <v>129</v>
+      </c>
+      <c r="L6" t="s">
+        <v>103</v>
       </c>
       <c r="M6">
-        <v>3.86</v>
+        <v>110</v>
       </c>
       <c r="N6">
-        <v>27.7</v>
+        <v>191</v>
       </c>
       <c r="O6">
-        <v>9.1300000000000008</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>13.87</v>
+        <v>90</v>
       </c>
       <c r="Q6">
-        <v>11.49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>147</v>
       </c>
       <c r="H7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
         <v>176</v>
       </c>
       <c r="K7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="L7" t="s">
-        <v>82</v>
-      </c>
-      <c r="M7" s="3">
-        <v>5.0036009302264111</v>
-      </c>
-      <c r="N7" s="3">
-        <v>9.580550685266056</v>
-      </c>
-      <c r="O7" s="3">
-        <v>3.6155636578885475</v>
-      </c>
-      <c r="P7" s="3">
-        <v>4.2959081426411982</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>3.2147361482584782</v>
+        <v>103</v>
+      </c>
+      <c r="M7">
+        <v>97</v>
+      </c>
+      <c r="N7">
+        <v>480</v>
+      </c>
+      <c r="O7">
+        <v>21</v>
+      </c>
+      <c r="P7">
+        <v>83</v>
+      </c>
+      <c r="Q7">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F8">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="s">
         <v>147</v>
       </c>
       <c r="H8" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J8" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K8" t="s">
         <v>131</v>
       </c>
-      <c r="L8" t="s">
-        <v>82</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0.9444479757744314</v>
-      </c>
-      <c r="N8" s="3">
-        <v>7.3802141343176784</v>
-      </c>
-      <c r="O8" s="3">
-        <v>2.7781266972668681</v>
-      </c>
-      <c r="P8" s="3">
-        <v>2.6090162342611549</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>2.4421237509841007</v>
+      <c r="L8">
+        <v>2009</v>
+      </c>
+      <c r="M8">
+        <v>16.7</v>
+      </c>
+      <c r="N8">
+        <v>40.5</v>
+      </c>
+      <c r="O8">
+        <v>6.8</v>
+      </c>
+      <c r="P8">
+        <v>24.4</v>
+      </c>
+      <c r="Q8">
+        <v>7.9</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G9" t="s">
         <v>147</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K9" t="s">
         <v>131</v>
       </c>
-      <c r="L9" t="s">
-        <v>82</v>
+      <c r="L9">
+        <v>2009</v>
       </c>
       <c r="M9">
-        <v>2.2000000000000002</v>
+        <v>2.7</v>
       </c>
       <c r="N9">
-        <v>8.4</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="O9">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="P9">
-        <v>3</v>
+        <v>6.1</v>
       </c>
       <c r="Q9">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="s">
         <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I10">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J10" t="s">
         <v>176</v>
@@ -1642,52 +1642,52 @@
       <c r="K10" t="s">
         <v>131</v>
       </c>
-      <c r="L10">
-        <v>2012</v>
-      </c>
-      <c r="M10">
-        <v>0.75</v>
-      </c>
-      <c r="N10">
-        <v>0.87</v>
-      </c>
-      <c r="O10">
-        <v>0.3</v>
-      </c>
-      <c r="P10">
-        <v>0.89</v>
-      </c>
-      <c r="Q10">
-        <v>0.46</v>
+      <c r="L10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0.9444479757744314</v>
+      </c>
+      <c r="N10" s="3">
+        <v>7.3802141343176784</v>
+      </c>
+      <c r="O10" s="3">
+        <v>2.7781266972668681</v>
+      </c>
+      <c r="P10" s="3">
+        <v>2.6090162342611549</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>2.4421237509841007</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
         <v>116</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
         <v>147</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I11">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J11" t="s">
         <v>176</v>
@@ -1695,52 +1695,52 @@
       <c r="K11" t="s">
         <v>131</v>
       </c>
-      <c r="L11">
-        <v>2012</v>
-      </c>
-      <c r="M11">
-        <v>0.66</v>
-      </c>
-      <c r="N11">
-        <v>0.88</v>
-      </c>
-      <c r="O11">
-        <v>0.24</v>
-      </c>
-      <c r="P11">
-        <v>0.77</v>
-      </c>
-      <c r="Q11">
-        <v>0.39</v>
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" s="3">
+        <v>5.0036009302264111</v>
+      </c>
+      <c r="N11" s="3">
+        <v>9.580550685266056</v>
+      </c>
+      <c r="O11" s="3">
+        <v>3.6155636578885475</v>
+      </c>
+      <c r="P11" s="3">
+        <v>4.2959081426411982</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>3.2147361482584782</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
         <v>147</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I12">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J12" t="s">
         <v>176</v>
@@ -1748,40 +1748,40 @@
       <c r="K12" t="s">
         <v>131</v>
       </c>
-      <c r="L12">
-        <v>2012</v>
+      <c r="L12" t="s">
+        <v>82</v>
       </c>
       <c r="M12">
-        <v>0.63</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N12">
-        <v>0.84</v>
+        <v>8.4</v>
       </c>
       <c r="O12">
-        <v>0.13</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>0.43</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>0.24</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1790,104 +1790,104 @@
         <v>147</v>
       </c>
       <c r="H13" t="s">
-        <v>133</v>
-      </c>
-      <c r="I13">
-        <v>52</v>
+        <v>134</v>
+      </c>
+      <c r="I13" t="s">
+        <v>179</v>
       </c>
       <c r="J13" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K13" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="M13">
-        <v>48</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N13">
-        <v>85</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="O13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>30</v>
+        <v>3.8</v>
       </c>
       <c r="Q13">
-        <v>15</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" t="s">
         <v>147</v>
       </c>
       <c r="H14" t="s">
-        <v>133</v>
-      </c>
-      <c r="I14">
-        <v>52</v>
+        <v>134</v>
+      </c>
+      <c r="I14" t="s">
+        <v>179</v>
       </c>
       <c r="J14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K14" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L14" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="M14">
-        <v>97</v>
+        <v>1.6</v>
       </c>
       <c r="N14">
-        <v>480</v>
+        <v>5.6</v>
       </c>
       <c r="O14">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>83</v>
+        <v>3.9</v>
       </c>
       <c r="Q14">
-        <v>40</v>
+        <v>1.1000000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -1896,157 +1896,157 @@
         <v>147</v>
       </c>
       <c r="H15" t="s">
-        <v>133</v>
-      </c>
-      <c r="I15">
-        <v>52</v>
+        <v>134</v>
+      </c>
+      <c r="I15" t="s">
+        <v>179</v>
       </c>
       <c r="J15" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K15" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L15" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="M15">
-        <v>89</v>
+        <v>2.7</v>
       </c>
       <c r="N15">
-        <v>204</v>
+        <v>10.7</v>
       </c>
       <c r="O15">
-        <v>16</v>
+        <v>2.7</v>
       </c>
       <c r="P15">
-        <v>61</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="Q15">
-        <v>41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
         <v>116</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" t="s">
         <v>147</v>
       </c>
       <c r="H16" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I16">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J16" t="s">
         <v>176</v>
       </c>
       <c r="K16" t="s">
-        <v>129</v>
-      </c>
-      <c r="L16" t="s">
-        <v>103</v>
+        <v>131</v>
+      </c>
+      <c r="L16">
+        <v>2012</v>
       </c>
       <c r="M16">
-        <v>110</v>
+        <v>0.75</v>
       </c>
       <c r="N16">
-        <v>191</v>
+        <v>0.87</v>
       </c>
       <c r="O16">
-        <v>24</v>
+        <v>0.3</v>
       </c>
       <c r="P16">
-        <v>90</v>
+        <v>0.89</v>
       </c>
       <c r="Q16">
-        <v>41</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B17" t="s">
         <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="E17" t="s">
         <v>116</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="G17" t="s">
         <v>147</v>
       </c>
       <c r="H17" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J17" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K17" t="s">
         <v>131</v>
       </c>
       <c r="L17">
-        <v>2003</v>
+        <v>2012</v>
       </c>
       <c r="M17">
-        <v>1.6</v>
+        <v>0.66</v>
       </c>
       <c r="N17">
-        <v>7</v>
+        <v>0.88</v>
       </c>
       <c r="O17">
-        <v>0.9</v>
+        <v>0.24</v>
       </c>
       <c r="P17">
-        <v>2.2999999999999998</v>
+        <v>0.77</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="E18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -2055,51 +2055,51 @@
         <v>147</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I18" t="s">
-        <v>179</v>
+        <v>136</v>
+      </c>
+      <c r="I18">
+        <v>48</v>
       </c>
       <c r="J18" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K18" t="s">
-        <v>114</v>
-      </c>
-      <c r="L18" t="s">
-        <v>118</v>
+        <v>131</v>
+      </c>
+      <c r="L18">
+        <v>2012</v>
       </c>
       <c r="M18">
-        <v>2.2000000000000002</v>
+        <v>0.63</v>
       </c>
       <c r="N18">
-        <v>4.9000000000000004</v>
+        <v>0.84</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0.13</v>
       </c>
       <c r="P18">
-        <v>3.8</v>
+        <v>0.43</v>
       </c>
       <c r="Q18">
-        <v>1.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -2108,197 +2108,201 @@
         <v>147</v>
       </c>
       <c r="H19" t="s">
-        <v>134</v>
-      </c>
-      <c r="I19" t="s">
-        <v>179</v>
+        <v>133</v>
+      </c>
+      <c r="I19">
+        <v>2</v>
       </c>
       <c r="J19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K19" t="s">
         <v>114</v>
       </c>
-      <c r="L19" t="s">
-        <v>118</v>
+      <c r="L19">
+        <v>2017</v>
       </c>
       <c r="M19">
-        <v>2.7</v>
+        <v>0.27300000000000002</v>
       </c>
       <c r="N19">
-        <v>10.7</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="O19">
-        <v>2.7</v>
+        <v>0.125</v>
       </c>
       <c r="P19">
-        <v>8.6999999999999993</v>
+        <v>0.432</v>
       </c>
       <c r="Q19">
-        <v>2.4</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" t="s">
         <v>147</v>
       </c>
       <c r="H20" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" t="s">
-        <v>179</v>
+        <v>133</v>
+      </c>
+      <c r="I20">
+        <v>2</v>
       </c>
       <c r="J20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K20" t="s">
         <v>114</v>
       </c>
-      <c r="L20" t="s">
-        <v>118</v>
+      <c r="L20">
+        <v>2017</v>
       </c>
       <c r="M20">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="N20">
-        <v>5.6</v>
-      </c>
-      <c r="O20">
-        <v>1</v>
+        <v>1.86</v>
+      </c>
+      <c r="O20" s="2">
+        <v>0.33</v>
       </c>
       <c r="P20">
-        <v>3.9</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>1.1000000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="E21" t="s">
         <v>116</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="G21" t="s">
         <v>147</v>
       </c>
       <c r="H21" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="L21">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="M21">
-        <v>1.38</v>
+        <v>0.76</v>
       </c>
       <c r="N21">
-        <v>1.86</v>
-      </c>
-      <c r="O21" s="2">
-        <v>0.33</v>
+        <v>2.87</v>
+      </c>
+      <c r="O21">
+        <v>0.47</v>
       </c>
       <c r="P21">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q21">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="G22" t="s">
         <v>147</v>
       </c>
       <c r="H22" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="I22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J22" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K22" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="L22">
-        <v>2017</v>
+        <v>2005</v>
       </c>
       <c r="M22">
-        <v>0.27300000000000002</v>
+        <v>0.98</v>
       </c>
       <c r="N22">
-        <v>0.80200000000000005</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="O22">
-        <v>0.125</v>
+        <v>0.48</v>
       </c>
       <c r="P22">
-        <v>0.432</v>
+        <v>1.28</v>
       </c>
       <c r="Q22">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q9" xr:uid="{96165E1C-E52F-4F48-86DB-7ECC2CD3F37C}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q22">
+    <sortCondition ref="A2:A22"/>
+    <sortCondition ref="E2:E22"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
